--- a/table/resources/sample/PointsAwardTurntable.xlsx
+++ b/table/resources/sample/PointsAwardTurntable.xlsx
@@ -27,8 +27,41 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+空值：表示默认数据
+有日期：对应月份读取的数据</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="21">
   <si>
     <t>序列ID</t>
   </si>
@@ -39,19 +72,28 @@
     <t>转盘奖励</t>
   </si>
   <si>
+    <t>开启时间</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
     <t>list&lt;int&gt;{_}</t>
   </si>
   <si>
+    <t>string</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
     <t>grid</t>
   </si>
   <si>
-    <t>getitem</t>
+    <t>getItem</t>
+  </si>
+  <si>
+    <t>time</t>
   </si>
   <si>
     <t>1022504_100</t>
@@ -88,13 +130,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -276,8 +319,19 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -293,6 +347,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -609,7 +687,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -633,16 +711,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -651,25 +729,13 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -678,21 +744,21 @@
     <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -732,8 +798,20 @@
     <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -749,6 +827,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -757,14 +838,32 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1112,454 +1211,576 @@
     <col min="1" max="1" width="7" style="4" customWidth="1"/>
     <col min="2" max="2" width="14.125" style="4" customWidth="1"/>
     <col min="3" max="3" width="20.375" style="4" customWidth="1"/>
-    <col min="4" max="7" width="14.5" style="5" customWidth="1"/>
+    <col min="4" max="4" width="14.5" style="5" customWidth="1"/>
+    <col min="5" max="7" width="14.5" style="6" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="6" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="6" t="s">
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="9"/>
+    </row>
+    <row r="5" s="2" customFormat="1" spans="1:7">
+      <c r="A5" s="12">
+        <v>1</v>
+      </c>
+      <c r="B5" s="12">
+        <v>0</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="13"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+    </row>
+    <row r="6" s="2" customFormat="1" spans="1:7">
+      <c r="A6" s="12">
+        <v>2</v>
+      </c>
+      <c r="B6" s="12">
+        <v>1</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="13"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+    </row>
+    <row r="7" s="2" customFormat="1" spans="1:7">
+      <c r="A7" s="12">
         <v>3</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="B7" s="12">
+        <v>2</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="13"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+    </row>
+    <row r="8" s="2" customFormat="1" spans="1:7">
+      <c r="A8" s="12">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="6" t="s">
+      <c r="B8" s="12">
+        <v>3</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="13"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+    </row>
+    <row r="9" s="3" customFormat="1" spans="1:9">
+      <c r="A9" s="12">
         <v>5</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B9" s="12">
+        <v>4</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="13"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="15"/>
+      <c r="I9" s="2"/>
+    </row>
+    <row r="10" s="3" customFormat="1" spans="1:9">
+      <c r="A10" s="12">
         <v>6</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="B10" s="12">
+        <v>5</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="13"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="15"/>
+      <c r="I10" s="2"/>
+    </row>
+    <row r="11" s="3" customFormat="1" spans="1:9">
+      <c r="A11" s="12">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-    </row>
-    <row r="5" s="2" customFormat="1" spans="1:7">
-      <c r="A5" s="2">
+      <c r="B11" s="12">
+        <v>6</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="13"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="15"/>
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" s="3" customFormat="1" spans="1:9">
+      <c r="A12" s="12">
+        <v>8</v>
+      </c>
+      <c r="B12" s="12">
+        <v>7</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="13"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="15"/>
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="12">
+        <v>9</v>
+      </c>
+      <c r="B13" s="12">
+        <v>8</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="13"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="I13" s="2"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="12">
+        <v>10</v>
+      </c>
+      <c r="B14" s="12">
+        <v>9</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="13"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="I14" s="2"/>
+    </row>
+    <row r="15" customFormat="1" spans="1:9">
+      <c r="A15" s="12">
+        <v>11</v>
+      </c>
+      <c r="B15" s="12">
+        <v>10</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="6"/>
+      <c r="I15" s="2"/>
+    </row>
+    <row r="16" s="3" customFormat="1" spans="1:9">
+      <c r="A16" s="12">
+        <v>12</v>
+      </c>
+      <c r="B16" s="12">
+        <v>11</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="13"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="15"/>
+      <c r="I16" s="2"/>
+    </row>
+    <row r="17" s="2" customFormat="1" spans="1:7">
+      <c r="A17" s="16">
+        <v>21</v>
+      </c>
+      <c r="B17" s="16">
+        <v>0</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="17">
+        <v>45931</v>
+      </c>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+    </row>
+    <row r="18" s="2" customFormat="1" spans="1:7">
+      <c r="A18" s="16">
+        <v>22</v>
+      </c>
+      <c r="B18" s="16">
         <v>1</v>
       </c>
-      <c r="B5" s="2">
-        <v>0</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="C18" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="17">
+        <v>45931</v>
+      </c>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+    </row>
+    <row r="19" s="2" customFormat="1" spans="1:7">
+      <c r="A19" s="16">
+        <v>23</v>
+      </c>
+      <c r="B19" s="16">
+        <v>2</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="17">
+        <v>45931</v>
+      </c>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+    </row>
+    <row r="20" s="2" customFormat="1" spans="1:7">
+      <c r="A20" s="16">
+        <v>24</v>
+      </c>
+      <c r="B20" s="16">
+        <v>3</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" s="17">
+        <v>45931</v>
+      </c>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+    </row>
+    <row r="21" s="3" customFormat="1" spans="1:9">
+      <c r="A21" s="16">
+        <v>25</v>
+      </c>
+      <c r="B21" s="16">
+        <v>4</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="17">
+        <v>45931</v>
+      </c>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="15"/>
+      <c r="I21" s="2"/>
+    </row>
+    <row r="22" s="3" customFormat="1" spans="1:9">
+      <c r="A22" s="16">
+        <v>26</v>
+      </c>
+      <c r="B22" s="16">
+        <v>5</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" s="17">
+        <v>45931</v>
+      </c>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="15"/>
+      <c r="I22" s="2"/>
+    </row>
+    <row r="23" s="3" customFormat="1" spans="1:9">
+      <c r="A23" s="16">
+        <v>27</v>
+      </c>
+      <c r="B23" s="16">
+        <v>6</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" s="17">
+        <v>45931</v>
+      </c>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="15"/>
+      <c r="I23" s="2"/>
+    </row>
+    <row r="24" s="3" customFormat="1" spans="1:9">
+      <c r="A24" s="16">
+        <v>28</v>
+      </c>
+      <c r="B24" s="16">
+        <v>7</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="17">
+        <v>45931</v>
+      </c>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="15"/>
+      <c r="I24" s="2"/>
+    </row>
+    <row r="25" s="3" customFormat="1" spans="1:9">
+      <c r="A25" s="16">
+        <v>29</v>
+      </c>
+      <c r="B25" s="16">
         <v>8</v>
       </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-    </row>
-    <row r="6" s="2" customFormat="1" spans="1:7">
-      <c r="A6" s="2">
-        <v>2</v>
-      </c>
-      <c r="B6" s="2">
-        <v>1</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="C25" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="17">
+        <v>45931</v>
+      </c>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="6"/>
+      <c r="I25" s="2"/>
+    </row>
+    <row r="26" s="3" customFormat="1" spans="1:9">
+      <c r="A26" s="16">
+        <v>30</v>
+      </c>
+      <c r="B26" s="16">
         <v>9</v>
       </c>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-    </row>
-    <row r="7" s="2" customFormat="1" spans="1:7">
-      <c r="A7" s="2">
-        <v>3</v>
-      </c>
-      <c r="B7" s="2">
-        <v>2</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="C26" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="17">
+        <v>45931</v>
+      </c>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="6"/>
+      <c r="I26" s="2"/>
+    </row>
+    <row r="27" customFormat="1" spans="1:9">
+      <c r="A27" s="16">
+        <v>31</v>
+      </c>
+      <c r="B27" s="16">
         <v>10</v>
       </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-    </row>
-    <row r="8" s="2" customFormat="1" spans="1:7">
-      <c r="A8" s="2">
-        <v>4</v>
-      </c>
-      <c r="B8" s="2">
-        <v>3</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="C27" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="17">
+        <v>45931</v>
+      </c>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="6"/>
+      <c r="I27" s="2"/>
+    </row>
+    <row r="28" s="3" customFormat="1" spans="1:9">
+      <c r="A28" s="16">
+        <v>32</v>
+      </c>
+      <c r="B28" s="16">
         <v>11</v>
       </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-    </row>
-    <row r="9" s="3" customFormat="1" spans="1:9">
-      <c r="A9" s="2">
-        <v>5</v>
-      </c>
-      <c r="B9" s="2">
-        <v>4</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="10"/>
-      <c r="I9" s="2"/>
-    </row>
-    <row r="10" s="3" customFormat="1" spans="1:9">
-      <c r="A10" s="2">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2">
-        <v>5</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="10"/>
-      <c r="I10" s="2"/>
-    </row>
-    <row r="11" s="3" customFormat="1" spans="1:9">
-      <c r="A11" s="2">
-        <v>7</v>
-      </c>
-      <c r="B11" s="2">
-        <v>6</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="10"/>
-      <c r="I11" s="2"/>
-    </row>
-    <row r="12" s="3" customFormat="1" spans="1:9">
-      <c r="A12" s="2">
-        <v>8</v>
-      </c>
-      <c r="B12" s="2">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="10"/>
-      <c r="I12" s="2"/>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="2">
-        <v>9</v>
-      </c>
-      <c r="B13" s="2">
-        <v>8</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="I13" s="2"/>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="2">
-        <v>10</v>
-      </c>
-      <c r="B14" s="2">
-        <v>9</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="I14" s="2"/>
-    </row>
-    <row r="15" customFormat="1" spans="1:9">
-      <c r="A15" s="2">
-        <v>11</v>
-      </c>
-      <c r="B15" s="2">
-        <v>10</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="C28" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="5"/>
-      <c r="I15" s="2"/>
-    </row>
-    <row r="16" s="3" customFormat="1" spans="1:9">
-      <c r="A16" s="2">
-        <v>12</v>
-      </c>
-      <c r="B16" s="2">
-        <v>11</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="10"/>
-      <c r="I16" s="2"/>
-    </row>
-    <row r="17" s="3" customFormat="1" spans="1:9">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="10"/>
-      <c r="I17" s="2"/>
-    </row>
-    <row r="18" s="3" customFormat="1" spans="1:9">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="10"/>
-      <c r="I18" s="2"/>
-    </row>
-    <row r="19" s="3" customFormat="1" spans="1:9">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="10"/>
-      <c r="I19" s="2"/>
-    </row>
-    <row r="20" s="3" customFormat="1" spans="1:9">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="I20" s="2"/>
-    </row>
-    <row r="22" s="3" customFormat="1" spans="1:7">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="10"/>
-    </row>
-    <row r="23" s="3" customFormat="1" spans="1:7">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="10"/>
-    </row>
-    <row r="24" s="3" customFormat="1" spans="1:7">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="10"/>
-    </row>
-    <row r="25" s="3" customFormat="1" spans="1:7">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="10"/>
-    </row>
-    <row r="26" s="3" customFormat="1" spans="1:7">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
+      <c r="D28" s="17">
+        <v>45931</v>
+      </c>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="15"/>
+      <c r="I28" s="2"/>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="14"/>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
     </row>
     <row r="44" spans="3:3">
       <c r="C44" s="2"/>
@@ -1582,6 +1803,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/table/resources/sample/PointsAwardTurntable.xlsx
+++ b/table/resources/sample/PointsAwardTurntable.xlsx
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
   <si>
     <t>序列ID</t>
   </si>
@@ -121,9 +121,6 @@
   </si>
   <si>
     <t>1022504_500</t>
-  </si>
-  <si>
-    <t>1022504_60</t>
   </si>
 </sst>
 </file>
@@ -320,18 +317,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="38">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -353,18 +350,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -687,7 +672,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -711,16 +696,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -729,89 +714,89 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -851,19 +836,16 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+    <xf numFmtId="14" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1205,7 +1187,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7" style="4" customWidth="1"/>
@@ -1274,10 +1256,10 @@
       <c r="C5" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
     </row>
     <row r="6" s="2" customFormat="1" spans="1:7">
       <c r="A6" s="12">
@@ -1289,10 +1271,10 @@
       <c r="C6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="13"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
     </row>
     <row r="7" s="2" customFormat="1" spans="1:7">
       <c r="A7" s="12">
@@ -1304,10 +1286,10 @@
       <c r="C7" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="13"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
     </row>
     <row r="8" s="2" customFormat="1" spans="1:7">
       <c r="A8" s="12">
@@ -1319,10 +1301,10 @@
       <c r="C8" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="13"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
     </row>
     <row r="9" s="3" customFormat="1" spans="1:9">
       <c r="A9" s="12">
@@ -1334,10 +1316,10 @@
       <c r="C9" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="15"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="14"/>
       <c r="I9" s="2"/>
     </row>
     <row r="10" s="3" customFormat="1" spans="1:9">
@@ -1350,10 +1332,10 @@
       <c r="C10" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="13"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="15"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="14"/>
       <c r="I10" s="2"/>
     </row>
     <row r="11" s="3" customFormat="1" spans="1:9">
@@ -1366,10 +1348,10 @@
       <c r="C11" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="13"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="15"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="14"/>
       <c r="I11" s="2"/>
     </row>
     <row r="12" s="3" customFormat="1" spans="1:9">
@@ -1382,10 +1364,10 @@
       <c r="C12" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="13"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="15"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="14"/>
       <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:9">
@@ -1398,9 +1380,9 @@
       <c r="C13" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="13"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
       <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:9">
@@ -1413,392 +1395,324 @@
       <c r="C14" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="13"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
       <c r="I14" s="2"/>
     </row>
-    <row r="15" customFormat="1" spans="1:9">
-      <c r="A15" s="12">
+    <row r="15" s="2" customFormat="1" spans="1:7">
+      <c r="A15" s="15">
+        <v>21</v>
+      </c>
+      <c r="B15" s="15">
+        <v>0</v>
+      </c>
+      <c r="C15" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="12">
-        <v>10</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="6"/>
-      <c r="I15" s="2"/>
-    </row>
-    <row r="16" s="3" customFormat="1" spans="1:9">
-      <c r="A16" s="12">
+      <c r="D15" s="16">
+        <v>45931</v>
+      </c>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+    </row>
+    <row r="16" s="2" customFormat="1" spans="1:7">
+      <c r="A16" s="15">
+        <v>22</v>
+      </c>
+      <c r="B16" s="15">
+        <v>1</v>
+      </c>
+      <c r="C16" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="12">
-        <v>11</v>
-      </c>
-      <c r="C16" s="12" t="s">
+      <c r="D16" s="16">
+        <v>45931</v>
+      </c>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+    </row>
+    <row r="17" s="2" customFormat="1" spans="1:7">
+      <c r="A17" s="15">
+        <v>23</v>
+      </c>
+      <c r="B17" s="15">
+        <v>2</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="16">
+        <v>45931</v>
+      </c>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+    </row>
+    <row r="18" s="2" customFormat="1" spans="1:7">
+      <c r="A18" s="15">
+        <v>24</v>
+      </c>
+      <c r="B18" s="15">
+        <v>3</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="16">
+        <v>45931</v>
+      </c>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+    </row>
+    <row r="19" s="3" customFormat="1" spans="1:9">
+      <c r="A19" s="15">
+        <v>25</v>
+      </c>
+      <c r="B19" s="15">
+        <v>4</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="16">
+        <v>45931</v>
+      </c>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="14"/>
+      <c r="I19" s="2"/>
+    </row>
+    <row r="20" s="3" customFormat="1" spans="1:9">
+      <c r="A20" s="15">
+        <v>26</v>
+      </c>
+      <c r="B20" s="15">
+        <v>5</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="16">
+        <v>45931</v>
+      </c>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="14"/>
+      <c r="I20" s="2"/>
+    </row>
+    <row r="21" s="3" customFormat="1" spans="1:9">
+      <c r="A21" s="15">
+        <v>27</v>
+      </c>
+      <c r="B21" s="15">
+        <v>6</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="16">
+        <v>45931</v>
+      </c>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="14"/>
+      <c r="I21" s="2"/>
+    </row>
+    <row r="22" s="3" customFormat="1" spans="1:9">
+      <c r="A22" s="15">
+        <v>28</v>
+      </c>
+      <c r="B22" s="15">
+        <v>7</v>
+      </c>
+      <c r="C22" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="13"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="15"/>
-      <c r="I16" s="2"/>
-    </row>
-    <row r="17" s="2" customFormat="1" spans="1:7">
-      <c r="A17" s="16">
-        <v>21</v>
-      </c>
-      <c r="B17" s="16">
-        <v>0</v>
-      </c>
-      <c r="C17" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="17">
+      <c r="D22" s="16">
         <v>45931</v>
       </c>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-    </row>
-    <row r="18" s="2" customFormat="1" spans="1:7">
-      <c r="A18" s="16">
-        <v>22</v>
-      </c>
-      <c r="B18" s="16">
-        <v>1</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" s="17">
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="14"/>
+      <c r="I22" s="2"/>
+    </row>
+    <row r="23" s="3" customFormat="1" spans="1:9">
+      <c r="A23" s="15">
+        <v>29</v>
+      </c>
+      <c r="B23" s="15">
+        <v>8</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="16">
         <v>45931</v>
       </c>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-    </row>
-    <row r="19" s="2" customFormat="1" spans="1:7">
-      <c r="A19" s="16">
-        <v>23</v>
-      </c>
-      <c r="B19" s="16">
-        <v>2</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" s="17">
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="6"/>
+      <c r="I23" s="2"/>
+    </row>
+    <row r="24" s="3" customFormat="1" spans="1:9">
+      <c r="A24" s="15">
+        <v>30</v>
+      </c>
+      <c r="B24" s="15">
+        <v>9</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="16">
         <v>45931</v>
       </c>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-    </row>
-    <row r="20" s="2" customFormat="1" spans="1:7">
-      <c r="A20" s="16">
-        <v>24</v>
-      </c>
-      <c r="B20" s="16">
-        <v>3</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D20" s="17">
-        <v>45931</v>
-      </c>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-    </row>
-    <row r="21" s="3" customFormat="1" spans="1:9">
-      <c r="A21" s="16">
-        <v>25</v>
-      </c>
-      <c r="B21" s="16">
-        <v>4</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="D21" s="17">
-        <v>45931</v>
-      </c>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="15"/>
-      <c r="I21" s="2"/>
-    </row>
-    <row r="22" s="3" customFormat="1" spans="1:9">
-      <c r="A22" s="16">
-        <v>26</v>
-      </c>
-      <c r="B22" s="16">
-        <v>5</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="D22" s="17">
-        <v>45931</v>
-      </c>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="15"/>
-      <c r="I22" s="2"/>
-    </row>
-    <row r="23" s="3" customFormat="1" spans="1:9">
-      <c r="A23" s="16">
-        <v>27</v>
-      </c>
-      <c r="B23" s="16">
-        <v>6</v>
-      </c>
-      <c r="C23" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D23" s="17">
-        <v>45931</v>
-      </c>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="15"/>
-      <c r="I23" s="2"/>
-    </row>
-    <row r="24" s="3" customFormat="1" spans="1:9">
-      <c r="A24" s="16">
-        <v>28</v>
-      </c>
-      <c r="B24" s="16">
-        <v>7</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="D24" s="17">
-        <v>45931</v>
-      </c>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="15"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="6"/>
       <c r="I24" s="2"/>
     </row>
-    <row r="25" s="3" customFormat="1" spans="1:9">
-      <c r="A25" s="16">
-        <v>29</v>
-      </c>
-      <c r="B25" s="16">
-        <v>8</v>
-      </c>
-      <c r="C25" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="D25" s="17">
-        <v>45931</v>
-      </c>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="6"/>
-      <c r="I25" s="2"/>
-    </row>
-    <row r="26" s="3" customFormat="1" spans="1:9">
-      <c r="A26" s="16">
-        <v>30</v>
-      </c>
-      <c r="B26" s="16">
-        <v>9</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D26" s="17">
-        <v>45931</v>
-      </c>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="6"/>
-      <c r="I26" s="2"/>
-    </row>
-    <row r="27" customFormat="1" spans="1:9">
-      <c r="A27" s="16">
-        <v>31</v>
-      </c>
-      <c r="B27" s="16">
-        <v>10</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="17">
-        <v>45931</v>
-      </c>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="6"/>
-      <c r="I27" s="2"/>
-    </row>
-    <row r="28" s="3" customFormat="1" spans="1:9">
-      <c r="A28" s="16">
-        <v>32</v>
-      </c>
-      <c r="B28" s="16">
-        <v>11</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="D28" s="17">
-        <v>45931</v>
-      </c>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="15"/>
-      <c r="I28" s="2"/>
+    <row r="25" spans="1:6">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+    </row>
+    <row r="40" spans="3:3">
       <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" s="2"/>
-      <c r="B41" s="2"/>
+    </row>
+    <row r="41" spans="3:3">
       <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="2"/>
-      <c r="B42" s="2"/>
+    </row>
+    <row r="42" spans="3:3">
       <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
+    </row>
+    <row r="43" spans="3:3">
       <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
     </row>
     <row r="44" spans="3:3">
       <c r="C44" s="2"/>
     </row>
     <row r="45" spans="3:3">
       <c r="C45" s="2"/>
-    </row>
-    <row r="46" spans="3:3">
-      <c r="C46" s="2"/>
-    </row>
-    <row r="47" spans="3:3">
-      <c r="C47" s="2"/>
-    </row>
-    <row r="48" spans="3:3">
-      <c r="C48" s="2"/>
-    </row>
-    <row r="49" spans="3:3">
-      <c r="C49" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/table/resources/sample/PointsAwardTurntable.xlsx
+++ b/table/resources/sample/PointsAwardTurntable.xlsx
@@ -33,6 +33,29 @@
     <author>Administrator</author>
   </authors>
   <commentList>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+最多配置1个道具，但积分就要不配置了，反之一样
+</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D1" authorId="0">
       <text>
         <r>
@@ -51,8 +74,53 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
+根据活动结束要清除数据，单独字段配置</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+填写道具Item资源文件夹中的道具名称</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
 空值：表示默认数据
-有日期：对应月份读取的数据</t>
+有日期：对应月份读取的数据
+注：必须“文本格式”</t>
         </r>
       </text>
     </comment>
@@ -61,7 +129,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="19">
   <si>
     <t>序列ID</t>
   </si>
@@ -69,7 +137,16 @@
     <t>转盘格子</t>
   </si>
   <si>
-    <t>转盘奖励</t>
+    <t>道具奖励</t>
+  </si>
+  <si>
+    <t>积分奖励</t>
+  </si>
+  <si>
+    <t>积分ICON</t>
+  </si>
+  <si>
+    <t>权重(万分比)</t>
   </si>
   <si>
     <t>开启时间</t>
@@ -93,46 +170,33 @@
     <t>getItem</t>
   </si>
   <si>
+    <t>integralNum</t>
+  </si>
+  <si>
+    <t>integralIcon</t>
+  </si>
+  <si>
+    <t>Probability</t>
+  </si>
+  <si>
     <t>time</t>
   </si>
   <si>
-    <t>1022504_100</t>
+    <t>itemicon_1022504.png</t>
   </si>
   <si>
-    <t>1022504_200</t>
-  </si>
-  <si>
-    <t>1022504_20</t>
-  </si>
-  <si>
-    <t>1022504_50</t>
-  </si>
-  <si>
-    <t>1022504_150</t>
-  </si>
-  <si>
-    <t>1022504_180</t>
-  </si>
-  <si>
-    <t>1022504_80</t>
-  </si>
-  <si>
-    <t>1022504_300</t>
-  </si>
-  <si>
-    <t>1022504_500</t>
+    <t>2025/10/01 00:00:00</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
   </numFmts>
   <fonts count="27">
     <font>
@@ -796,7 +860,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -812,7 +876,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -824,28 +888,46 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1187,18 +1269,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7" style="4" customWidth="1"/>
-    <col min="2" max="2" width="14.125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="20.375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="14.5" style="5" customWidth="1"/>
-    <col min="5" max="7" width="14.5" style="6" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="4"/>
+    <col min="2" max="2" width="8.875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="13.875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="13.125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="23.625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="12.25" style="4" customWidth="1"/>
+    <col min="7" max="7" width="21.25" style="5" customWidth="1"/>
+    <col min="8" max="10" width="14.5" style="6" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:7">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1211,508 +1296,741 @@
       <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="7" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>7</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>11</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
-      <c r="D4" s="9"/>
-    </row>
-    <row r="5" s="2" customFormat="1" spans="1:7">
-      <c r="A5" s="12">
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="11"/>
+    </row>
+    <row r="5" s="2" customFormat="1" spans="1:10">
+      <c r="A5" s="16">
         <v>1</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="16">
         <v>0</v>
       </c>
-      <c r="C5" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-    </row>
-    <row r="6" s="2" customFormat="1" spans="1:7">
-      <c r="A6" s="12">
+      <c r="C5" s="16"/>
+      <c r="D5" s="16">
+        <v>10</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="16">
+        <v>1000</v>
+      </c>
+      <c r="G5" s="17"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="18"/>
+    </row>
+    <row r="6" s="2" customFormat="1" spans="1:10">
+      <c r="A6" s="16">
         <v>2</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="16">
         <v>1</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-    </row>
-    <row r="7" s="2" customFormat="1" spans="1:7">
-      <c r="A7" s="12">
+      <c r="C6" s="16"/>
+      <c r="D6" s="16">
+        <v>50</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="16">
+        <v>1000</v>
+      </c>
+      <c r="G6" s="17"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+    </row>
+    <row r="7" s="2" customFormat="1" spans="1:10">
+      <c r="A7" s="16">
         <v>3</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="16">
         <v>2</v>
       </c>
-      <c r="C7" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="12"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-    </row>
-    <row r="8" s="2" customFormat="1" spans="1:7">
-      <c r="A8" s="12">
+      <c r="C7" s="16"/>
+      <c r="D7" s="16">
+        <v>30</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="16">
+        <v>1000</v>
+      </c>
+      <c r="G7" s="17"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="18"/>
+    </row>
+    <row r="8" s="2" customFormat="1" spans="1:10">
+      <c r="A8" s="16">
         <v>4</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="16">
         <v>3</v>
       </c>
-      <c r="C8" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-    </row>
-    <row r="9" s="3" customFormat="1" spans="1:9">
-      <c r="A9" s="12">
+      <c r="C8" s="16"/>
+      <c r="D8" s="16">
+        <v>40</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="16">
+        <v>1000</v>
+      </c>
+      <c r="G8" s="17"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+    </row>
+    <row r="9" s="3" customFormat="1" spans="1:12">
+      <c r="A9" s="16">
         <v>5</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="16">
         <v>4</v>
       </c>
-      <c r="C9" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="12"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="14"/>
-      <c r="I9" s="2"/>
-    </row>
-    <row r="10" s="3" customFormat="1" spans="1:9">
-      <c r="A10" s="12">
+      <c r="C9" s="16"/>
+      <c r="D9" s="16">
+        <v>20</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="16">
+        <v>1000</v>
+      </c>
+      <c r="G9" s="17"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="22"/>
+      <c r="L9" s="2"/>
+    </row>
+    <row r="10" s="3" customFormat="1" spans="1:12">
+      <c r="A10" s="16">
         <v>6</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="16">
         <v>5</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="12"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="14"/>
-      <c r="I10" s="2"/>
-    </row>
-    <row r="11" s="3" customFormat="1" spans="1:9">
-      <c r="A11" s="12">
+      <c r="C10" s="16"/>
+      <c r="D10" s="16">
+        <v>80</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="16">
+        <v>1000</v>
+      </c>
+      <c r="G10" s="17"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="22"/>
+      <c r="L10" s="2"/>
+    </row>
+    <row r="11" s="3" customFormat="1" spans="1:12">
+      <c r="A11" s="16">
         <v>7</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="16">
         <v>6</v>
       </c>
-      <c r="C11" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" s="12"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="14"/>
-      <c r="I11" s="2"/>
-    </row>
-    <row r="12" s="3" customFormat="1" spans="1:9">
-      <c r="A12" s="12">
+      <c r="C11" s="16"/>
+      <c r="D11" s="16">
+        <v>60</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="16">
+        <v>1000</v>
+      </c>
+      <c r="G11" s="17"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="22"/>
+      <c r="L11" s="2"/>
+    </row>
+    <row r="12" s="3" customFormat="1" spans="1:12">
+      <c r="A12" s="16">
         <v>8</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="16">
         <v>7</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="16"/>
+      <c r="D12" s="16">
+        <v>50</v>
+      </c>
+      <c r="E12" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="12"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="14"/>
-      <c r="I12" s="2"/>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="12">
+      <c r="F12" s="16">
+        <v>1000</v>
+      </c>
+      <c r="G12" s="17"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="18"/>
+      <c r="J12" s="22"/>
+      <c r="L12" s="2"/>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" s="16">
         <v>9</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="16">
         <v>8</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="16"/>
+      <c r="D13" s="16">
+        <v>100</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="16">
+        <v>1000</v>
+      </c>
+      <c r="G13" s="17"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
+      <c r="L13" s="2"/>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="16">
+        <v>10</v>
+      </c>
+      <c r="B14" s="16">
+        <v>9</v>
+      </c>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16">
+        <v>150</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="16">
+        <v>1000</v>
+      </c>
+      <c r="G14" s="17"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
+      <c r="L14" s="2"/>
+    </row>
+    <row r="15" s="2" customFormat="1" spans="1:10">
+      <c r="A15" s="19">
+        <v>21</v>
+      </c>
+      <c r="B15" s="19">
+        <v>0</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19">
+        <v>20</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="19">
+        <v>1000</v>
+      </c>
+      <c r="G15" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="12"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="I13" s="2"/>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="12">
-        <v>10</v>
-      </c>
-      <c r="B14" s="12">
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="18"/>
+    </row>
+    <row r="16" s="2" customFormat="1" spans="1:10">
+      <c r="A16" s="19">
+        <v>22</v>
+      </c>
+      <c r="B16" s="19">
+        <v>1</v>
+      </c>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19">
+        <v>60</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="19">
+        <v>1000</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="18"/>
+    </row>
+    <row r="17" s="2" customFormat="1" spans="1:10">
+      <c r="A17" s="19">
+        <v>23</v>
+      </c>
+      <c r="B17" s="19">
+        <v>2</v>
+      </c>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19">
+        <v>40</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="19">
+        <v>1000</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="18"/>
+    </row>
+    <row r="18" s="2" customFormat="1" spans="1:10">
+      <c r="A18" s="19">
+        <v>24</v>
+      </c>
+      <c r="B18" s="19">
+        <v>3</v>
+      </c>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19">
+        <v>80</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="19">
+        <v>1000</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="18"/>
+    </row>
+    <row r="19" s="3" customFormat="1" spans="1:12">
+      <c r="A19" s="19">
+        <v>25</v>
+      </c>
+      <c r="B19" s="19">
+        <v>4</v>
+      </c>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19">
+        <v>70</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="19">
+        <v>1000</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="22"/>
+      <c r="L19" s="2"/>
+    </row>
+    <row r="20" s="3" customFormat="1" spans="1:12">
+      <c r="A20" s="19">
+        <v>26</v>
+      </c>
+      <c r="B20" s="19">
+        <v>5</v>
+      </c>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19">
+        <v>120</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="19">
+        <v>1000</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H20" s="18"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="22"/>
+      <c r="L20" s="2"/>
+    </row>
+    <row r="21" s="3" customFormat="1" spans="1:12">
+      <c r="A21" s="19">
+        <v>27</v>
+      </c>
+      <c r="B21" s="19">
+        <v>6</v>
+      </c>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19">
+        <v>160</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="19">
+        <v>1000</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="22"/>
+      <c r="L21" s="2"/>
+    </row>
+    <row r="22" s="3" customFormat="1" spans="1:12">
+      <c r="A22" s="19">
+        <v>28</v>
+      </c>
+      <c r="B22" s="19">
+        <v>7</v>
+      </c>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19">
+        <v>80</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" s="19">
+        <v>1000</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="22"/>
+      <c r="L22" s="2"/>
+    </row>
+    <row r="23" s="3" customFormat="1" spans="1:12">
+      <c r="A23" s="19">
+        <v>29</v>
+      </c>
+      <c r="B23" s="19">
+        <v>8</v>
+      </c>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19">
+        <v>100</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" s="19">
+        <v>1000</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="6"/>
+      <c r="L23" s="2"/>
+    </row>
+    <row r="24" s="3" customFormat="1" spans="1:12">
+      <c r="A24" s="19">
+        <v>30</v>
+      </c>
+      <c r="B24" s="19">
         <v>9</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="12"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="I14" s="2"/>
-    </row>
-    <row r="15" s="2" customFormat="1" spans="1:7">
-      <c r="A15" s="15">
-        <v>21</v>
-      </c>
-      <c r="B15" s="15">
-        <v>0</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" s="16">
-        <v>45931</v>
-      </c>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-    </row>
-    <row r="16" s="2" customFormat="1" spans="1:7">
-      <c r="A16" s="15">
-        <v>22</v>
-      </c>
-      <c r="B16" s="15">
-        <v>1</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="16">
-        <v>45931</v>
-      </c>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-    </row>
-    <row r="17" s="2" customFormat="1" spans="1:7">
-      <c r="A17" s="15">
-        <v>23</v>
-      </c>
-      <c r="B17" s="15">
-        <v>2</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="16">
-        <v>45931</v>
-      </c>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-    </row>
-    <row r="18" s="2" customFormat="1" spans="1:7">
-      <c r="A18" s="15">
-        <v>24</v>
-      </c>
-      <c r="B18" s="15">
-        <v>3</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="D18" s="16">
-        <v>45931</v>
-      </c>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-    </row>
-    <row r="19" s="3" customFormat="1" spans="1:9">
-      <c r="A19" s="15">
-        <v>25</v>
-      </c>
-      <c r="B19" s="15">
-        <v>4</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" s="16">
-        <v>45931</v>
-      </c>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="14"/>
-      <c r="I19" s="2"/>
-    </row>
-    <row r="20" s="3" customFormat="1" spans="1:9">
-      <c r="A20" s="15">
-        <v>26</v>
-      </c>
-      <c r="B20" s="15">
-        <v>5</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="D20" s="16">
-        <v>45931</v>
-      </c>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="14"/>
-      <c r="I20" s="2"/>
-    </row>
-    <row r="21" s="3" customFormat="1" spans="1:9">
-      <c r="A21" s="15">
-        <v>27</v>
-      </c>
-      <c r="B21" s="15">
-        <v>6</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="D21" s="16">
-        <v>45931</v>
-      </c>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="14"/>
-      <c r="I21" s="2"/>
-    </row>
-    <row r="22" s="3" customFormat="1" spans="1:9">
-      <c r="A22" s="15">
-        <v>28</v>
-      </c>
-      <c r="B22" s="15">
-        <v>7</v>
-      </c>
-      <c r="C22" s="15" t="s">
+      <c r="C24" s="19"/>
+      <c r="D24" s="19">
+        <v>150</v>
+      </c>
+      <c r="E24" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="16">
-        <v>45931</v>
-      </c>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="14"/>
-      <c r="I22" s="2"/>
-    </row>
-    <row r="23" s="3" customFormat="1" spans="1:9">
-      <c r="A23" s="15">
-        <v>29</v>
-      </c>
-      <c r="B23" s="15">
-        <v>8</v>
-      </c>
-      <c r="C23" s="15" t="s">
+      <c r="F24" s="19">
+        <v>1000</v>
+      </c>
+      <c r="G24" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="16">
-        <v>45931</v>
-      </c>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="6"/>
-      <c r="I23" s="2"/>
-    </row>
-    <row r="24" s="3" customFormat="1" spans="1:9">
-      <c r="A24" s="15">
-        <v>30</v>
-      </c>
-      <c r="B24" s="15">
-        <v>9</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D24" s="16">
-        <v>45931</v>
-      </c>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="6"/>
-      <c r="I24" s="2"/>
-    </row>
-    <row r="25" spans="1:6">
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="6"/>
+      <c r="L24" s="2"/>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-    </row>
-    <row r="26" spans="1:6">
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-    </row>
-    <row r="27" spans="1:6">
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-    </row>
-    <row r="28" spans="1:6">
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="18"/>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-    </row>
-    <row r="29" spans="1:6">
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-    </row>
-    <row r="30" spans="1:6">
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="18"/>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-    </row>
-    <row r="31" spans="1:6">
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="18"/>
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-    </row>
-    <row r="32" spans="1:6">
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="18"/>
+    </row>
+    <row r="32" spans="1:9">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-    </row>
-    <row r="33" spans="1:6">
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-    </row>
-    <row r="34" spans="1:6">
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="18"/>
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-    </row>
-    <row r="35" spans="1:6">
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="21"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="18"/>
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-    </row>
-    <row r="36" spans="1:6">
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="18"/>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-    </row>
-    <row r="37" spans="1:6">
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="18"/>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-    </row>
-    <row r="38" spans="1:6">
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="21"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="18"/>
+    </row>
+    <row r="38" spans="1:9">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-    </row>
-    <row r="39" spans="1:6">
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="18"/>
+    </row>
+    <row r="39" spans="1:9">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-    </row>
-    <row r="40" spans="3:3">
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="21"/>
+      <c r="H39" s="18"/>
+      <c r="I39" s="18"/>
+    </row>
+    <row r="40" spans="3:6">
       <c r="C40" s="2"/>
-    </row>
-    <row r="41" spans="3:3">
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+    </row>
+    <row r="41" spans="3:6">
       <c r="C41" s="2"/>
-    </row>
-    <row r="42" spans="3:3">
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+    </row>
+    <row r="42" spans="3:6">
       <c r="C42" s="2"/>
-    </row>
-    <row r="43" spans="3:3">
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+    </row>
+    <row r="43" spans="3:6">
       <c r="C43" s="2"/>
-    </row>
-    <row r="44" spans="3:3">
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+    </row>
+    <row r="44" spans="3:6">
       <c r="C44" s="2"/>
-    </row>
-    <row r="45" spans="3:3">
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+    </row>
+    <row r="45" spans="3:6">
       <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/table/resources/sample/PointsAwardTurntable.xlsx
+++ b/table/resources/sample/PointsAwardTurntable.xlsx
@@ -1370,13 +1370,13 @@
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="16">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>17</v>
       </c>
       <c r="F5" s="16">
-        <v>1000</v>
+        <v>2421</v>
       </c>
       <c r="G5" s="17"/>
       <c r="H5" s="18"/>
@@ -1392,13 +1392,13 @@
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E6" s="16" t="s">
         <v>17</v>
       </c>
       <c r="F6" s="16">
-        <v>1000</v>
+        <v>2017</v>
       </c>
       <c r="G6" s="17"/>
       <c r="H6" s="18"/>
@@ -1414,13 +1414,13 @@
       </c>
       <c r="C7" s="16"/>
       <c r="D7" s="16">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>17</v>
       </c>
       <c r="F7" s="16">
-        <v>1000</v>
+        <v>1513</v>
       </c>
       <c r="G7" s="17"/>
       <c r="H7" s="18"/>
@@ -1436,13 +1436,13 @@
       </c>
       <c r="C8" s="16"/>
       <c r="D8" s="16">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="E8" s="16" t="s">
         <v>17</v>
       </c>
       <c r="F8" s="16">
-        <v>1000</v>
+        <v>1210</v>
       </c>
       <c r="G8" s="17"/>
       <c r="H8" s="18"/>
@@ -1458,13 +1458,13 @@
       </c>
       <c r="C9" s="16"/>
       <c r="D9" s="16">
-        <v>20</v>
+        <v>130</v>
       </c>
       <c r="E9" s="16" t="s">
         <v>17</v>
       </c>
       <c r="F9" s="16">
-        <v>1000</v>
+        <v>928</v>
       </c>
       <c r="G9" s="17"/>
       <c r="H9" s="18"/>
@@ -1481,13 +1481,13 @@
       </c>
       <c r="C10" s="16"/>
       <c r="D10" s="16">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="E10" s="16" t="s">
         <v>17</v>
       </c>
       <c r="F10" s="16">
-        <v>1000</v>
+        <v>753</v>
       </c>
       <c r="G10" s="17"/>
       <c r="H10" s="18"/>
@@ -1504,13 +1504,13 @@
       </c>
       <c r="C11" s="16"/>
       <c r="D11" s="16">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="E11" s="16" t="s">
         <v>17</v>
       </c>
       <c r="F11" s="16">
-        <v>1000</v>
+        <v>484</v>
       </c>
       <c r="G11" s="17"/>
       <c r="H11" s="18"/>
@@ -1527,13 +1527,13 @@
       </c>
       <c r="C12" s="16"/>
       <c r="D12" s="16">
-        <v>50</v>
+        <v>240</v>
       </c>
       <c r="E12" s="16" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="16">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="G12" s="17"/>
       <c r="H12" s="18"/>
@@ -1550,13 +1550,13 @@
       </c>
       <c r="C13" s="16"/>
       <c r="D13" s="16">
-        <v>100</v>
+        <v>280</v>
       </c>
       <c r="E13" s="16" t="s">
         <v>17</v>
       </c>
       <c r="F13" s="16">
-        <v>1000</v>
+        <v>215</v>
       </c>
       <c r="G13" s="17"/>
       <c r="H13" s="18"/>
@@ -1572,13 +1572,13 @@
       </c>
       <c r="C14" s="16"/>
       <c r="D14" s="16">
-        <v>150</v>
+        <v>320</v>
       </c>
       <c r="E14" s="16" t="s">
         <v>17</v>
       </c>
       <c r="F14" s="16">
-        <v>1000</v>
+        <v>108</v>
       </c>
       <c r="G14" s="17"/>
       <c r="H14" s="18"/>
@@ -1594,13 +1594,13 @@
       </c>
       <c r="C15" s="19"/>
       <c r="D15" s="19">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E15" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F15" s="19">
-        <v>1000</v>
+        <v>2421</v>
       </c>
       <c r="G15" s="20" t="s">
         <v>18</v>
@@ -1624,7 +1624,7 @@
         <v>17</v>
       </c>
       <c r="F16" s="19">
-        <v>1000</v>
+        <v>2017</v>
       </c>
       <c r="G16" s="20" t="s">
         <v>18</v>
@@ -1642,13 +1642,13 @@
       </c>
       <c r="C17" s="19"/>
       <c r="D17" s="19">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="E17" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F17" s="19">
-        <v>1000</v>
+        <v>1513</v>
       </c>
       <c r="G17" s="20" t="s">
         <v>18</v>
@@ -1666,13 +1666,13 @@
       </c>
       <c r="C18" s="19"/>
       <c r="D18" s="19">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E18" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F18" s="19">
-        <v>1000</v>
+        <v>1210</v>
       </c>
       <c r="G18" s="20" t="s">
         <v>18</v>
@@ -1690,13 +1690,13 @@
       </c>
       <c r="C19" s="19"/>
       <c r="D19" s="19">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="E19" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F19" s="19">
-        <v>1000</v>
+        <v>928</v>
       </c>
       <c r="G19" s="20" t="s">
         <v>18</v>
@@ -1715,13 +1715,13 @@
       </c>
       <c r="C20" s="19"/>
       <c r="D20" s="19">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="E20" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F20" s="19">
-        <v>1000</v>
+        <v>753</v>
       </c>
       <c r="G20" s="20" t="s">
         <v>18</v>
@@ -1740,13 +1740,13 @@
       </c>
       <c r="C21" s="19"/>
       <c r="D21" s="19">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="E21" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F21" s="19">
-        <v>1000</v>
+        <v>484</v>
       </c>
       <c r="G21" s="20" t="s">
         <v>18</v>
@@ -1765,13 +1765,13 @@
       </c>
       <c r="C22" s="19"/>
       <c r="D22" s="19">
-        <v>80</v>
+        <v>240</v>
       </c>
       <c r="E22" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F22" s="19">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="G22" s="20" t="s">
         <v>18</v>
@@ -1790,13 +1790,13 @@
       </c>
       <c r="C23" s="19"/>
       <c r="D23" s="19">
-        <v>100</v>
+        <v>280</v>
       </c>
       <c r="E23" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F23" s="19">
-        <v>1000</v>
+        <v>215</v>
       </c>
       <c r="G23" s="20" t="s">
         <v>18</v>
@@ -1815,13 +1815,13 @@
       </c>
       <c r="C24" s="19"/>
       <c r="D24" s="19">
-        <v>150</v>
+        <v>320</v>
       </c>
       <c r="E24" s="19" t="s">
         <v>17</v>
       </c>
       <c r="F24" s="19">
-        <v>1000</v>
+        <v>108</v>
       </c>
       <c r="G24" s="20" t="s">
         <v>18</v>

--- a/table/resources/sample/PointsAwardTurntable.xlsx
+++ b/table/resources/sample/PointsAwardTurntable.xlsx
@@ -918,6 +918,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -925,9 +928,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1283,7 +1283,7 @@
     <col min="11" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:12">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1306,7 +1306,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:12">
       <c r="A2" s="7" t="s">
         <v>7</v>
       </c>
@@ -1329,7 +1329,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:12">
       <c r="A3" s="7" t="s">
         <v>10</v>
       </c>
@@ -1352,7 +1352,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:12">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -1361,7 +1361,7 @@
       <c r="F4" s="7"/>
       <c r="G4" s="11"/>
     </row>
-    <row r="5" s="2" customFormat="1" spans="1:10">
+    <row r="5" s="2" customFormat="1" spans="1:12">
       <c r="A5" s="16">
         <v>1</v>
       </c>
@@ -1376,14 +1376,14 @@
         <v>17</v>
       </c>
       <c r="F5" s="16">
-        <v>2421</v>
+        <v>1786</v>
       </c>
       <c r="G5" s="17"/>
       <c r="H5" s="18"/>
       <c r="I5" s="18"/>
       <c r="J5" s="18"/>
     </row>
-    <row r="6" s="2" customFormat="1" spans="1:10">
+    <row r="6" s="2" customFormat="1" spans="1:12">
       <c r="A6" s="16">
         <v>2</v>
       </c>
@@ -1398,14 +1398,14 @@
         <v>17</v>
       </c>
       <c r="F6" s="16">
-        <v>2017</v>
+        <v>1786</v>
       </c>
       <c r="G6" s="17"/>
       <c r="H6" s="18"/>
       <c r="I6" s="18"/>
       <c r="J6" s="18"/>
     </row>
-    <row r="7" s="2" customFormat="1" spans="1:10">
+    <row r="7" s="2" customFormat="1" spans="1:12">
       <c r="A7" s="16">
         <v>3</v>
       </c>
@@ -1420,14 +1420,14 @@
         <v>17</v>
       </c>
       <c r="F7" s="16">
-        <v>1513</v>
+        <v>1786</v>
       </c>
       <c r="G7" s="17"/>
       <c r="H7" s="18"/>
       <c r="I7" s="18"/>
       <c r="J7" s="18"/>
     </row>
-    <row r="8" s="2" customFormat="1" spans="1:10">
+    <row r="8" s="2" customFormat="1" spans="1:12">
       <c r="A8" s="16">
         <v>4</v>
       </c>
@@ -1442,7 +1442,7 @@
         <v>17</v>
       </c>
       <c r="F8" s="16">
-        <v>1210</v>
+        <v>1488</v>
       </c>
       <c r="G8" s="17"/>
       <c r="H8" s="18"/>
@@ -1458,18 +1458,18 @@
       </c>
       <c r="C9" s="16"/>
       <c r="D9" s="16">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="E9" s="16" t="s">
         <v>17</v>
       </c>
       <c r="F9" s="16">
-        <v>928</v>
+        <v>1488</v>
       </c>
       <c r="G9" s="17"/>
       <c r="H9" s="18"/>
       <c r="I9" s="18"/>
-      <c r="J9" s="22"/>
+      <c r="J9" s="19"/>
       <c r="L9" s="2"/>
     </row>
     <row r="10" s="3" customFormat="1" spans="1:12">
@@ -1481,18 +1481,18 @@
       </c>
       <c r="C10" s="16"/>
       <c r="D10" s="16">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="E10" s="16" t="s">
         <v>17</v>
       </c>
       <c r="F10" s="16">
-        <v>753</v>
+        <v>893</v>
       </c>
       <c r="G10" s="17"/>
       <c r="H10" s="18"/>
       <c r="I10" s="18"/>
-      <c r="J10" s="22"/>
+      <c r="J10" s="19"/>
       <c r="L10" s="2"/>
     </row>
     <row r="11" s="3" customFormat="1" spans="1:12">
@@ -1510,12 +1510,12 @@
         <v>17</v>
       </c>
       <c r="F11" s="16">
-        <v>484</v>
+        <v>595</v>
       </c>
       <c r="G11" s="17"/>
       <c r="H11" s="18"/>
       <c r="I11" s="18"/>
-      <c r="J11" s="22"/>
+      <c r="J11" s="19"/>
       <c r="L11" s="2"/>
     </row>
     <row r="12" s="3" customFormat="1" spans="1:12">
@@ -1527,18 +1527,18 @@
       </c>
       <c r="C12" s="16"/>
       <c r="D12" s="16">
-        <v>240</v>
+        <v>400</v>
       </c>
       <c r="E12" s="16" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="16">
-        <v>350</v>
+        <v>149</v>
       </c>
       <c r="G12" s="17"/>
       <c r="H12" s="18"/>
       <c r="I12" s="18"/>
-      <c r="J12" s="22"/>
+      <c r="J12" s="19"/>
       <c r="L12" s="2"/>
     </row>
     <row r="13" spans="1:12">
@@ -1550,13 +1550,13 @@
       </c>
       <c r="C13" s="16"/>
       <c r="D13" s="16">
-        <v>280</v>
+        <v>600</v>
       </c>
       <c r="E13" s="16" t="s">
         <v>17</v>
       </c>
       <c r="F13" s="16">
-        <v>215</v>
+        <v>30</v>
       </c>
       <c r="G13" s="17"/>
       <c r="H13" s="18"/>
@@ -1572,109 +1572,109 @@
       </c>
       <c r="C14" s="16"/>
       <c r="D14" s="16">
-        <v>320</v>
+        <v>1200</v>
       </c>
       <c r="E14" s="16" t="s">
         <v>17</v>
       </c>
       <c r="F14" s="16">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="G14" s="17"/>
       <c r="H14" s="18"/>
       <c r="I14" s="18"/>
       <c r="L14" s="2"/>
     </row>
-    <row r="15" s="2" customFormat="1" spans="1:10">
-      <c r="A15" s="19">
+    <row r="15" s="2" customFormat="1" spans="1:12">
+      <c r="A15" s="20">
         <v>21</v>
       </c>
-      <c r="B15" s="19">
+      <c r="B15" s="20">
         <v>0</v>
       </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19">
+      <c r="C15" s="20"/>
+      <c r="D15" s="20">
         <v>50</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="19">
-        <v>2421</v>
-      </c>
-      <c r="G15" s="20" t="s">
+      <c r="F15" s="20">
+        <v>1786</v>
+      </c>
+      <c r="G15" s="21" t="s">
         <v>18</v>
       </c>
       <c r="H15" s="18"/>
       <c r="I15" s="18"/>
       <c r="J15" s="18"/>
     </row>
-    <row r="16" s="2" customFormat="1" spans="1:10">
-      <c r="A16" s="19">
+    <row r="16" s="2" customFormat="1" spans="1:12">
+      <c r="A16" s="20">
         <v>22</v>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="20">
         <v>1</v>
       </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19">
+      <c r="C16" s="20"/>
+      <c r="D16" s="20">
         <v>60</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="E16" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="F16" s="19">
-        <v>2017</v>
-      </c>
-      <c r="G16" s="20" t="s">
+      <c r="F16" s="20">
+        <v>1786</v>
+      </c>
+      <c r="G16" s="21" t="s">
         <v>18</v>
       </c>
       <c r="H16" s="18"/>
       <c r="I16" s="18"/>
       <c r="J16" s="18"/>
     </row>
-    <row r="17" s="2" customFormat="1" spans="1:10">
-      <c r="A17" s="19">
+    <row r="17" s="2" customFormat="1" spans="1:12">
+      <c r="A17" s="20">
         <v>23</v>
       </c>
-      <c r="B17" s="19">
+      <c r="B17" s="20">
         <v>2</v>
       </c>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19">
+      <c r="C17" s="20"/>
+      <c r="D17" s="20">
         <v>80</v>
       </c>
-      <c r="E17" s="19" t="s">
+      <c r="E17" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="F17" s="19">
-        <v>1513</v>
-      </c>
-      <c r="G17" s="20" t="s">
+      <c r="F17" s="20">
+        <v>1786</v>
+      </c>
+      <c r="G17" s="21" t="s">
         <v>18</v>
       </c>
       <c r="H17" s="18"/>
       <c r="I17" s="18"/>
       <c r="J17" s="18"/>
     </row>
-    <row r="18" s="2" customFormat="1" spans="1:10">
-      <c r="A18" s="19">
+    <row r="18" s="2" customFormat="1" spans="1:12">
+      <c r="A18" s="20">
         <v>24</v>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="20">
         <v>3</v>
       </c>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19">
+      <c r="C18" s="20"/>
+      <c r="D18" s="20">
         <v>100</v>
       </c>
-      <c r="E18" s="19" t="s">
+      <c r="E18" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="F18" s="19">
-        <v>1210</v>
-      </c>
-      <c r="G18" s="20" t="s">
+      <c r="F18" s="20">
+        <v>1488</v>
+      </c>
+      <c r="G18" s="21" t="s">
         <v>18</v>
       </c>
       <c r="H18" s="18"/>
@@ -1682,123 +1682,123 @@
       <c r="J18" s="18"/>
     </row>
     <row r="19" s="3" customFormat="1" spans="1:12">
-      <c r="A19" s="19">
+      <c r="A19" s="20">
         <v>25</v>
       </c>
-      <c r="B19" s="19">
+      <c r="B19" s="20">
         <v>4</v>
       </c>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19">
-        <v>130</v>
-      </c>
-      <c r="E19" s="19" t="s">
+      <c r="C19" s="20"/>
+      <c r="D19" s="20">
+        <v>120</v>
+      </c>
+      <c r="E19" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="F19" s="19">
-        <v>928</v>
-      </c>
-      <c r="G19" s="20" t="s">
+      <c r="F19" s="20">
+        <v>1488</v>
+      </c>
+      <c r="G19" s="21" t="s">
         <v>18</v>
       </c>
       <c r="H19" s="18"/>
       <c r="I19" s="18"/>
-      <c r="J19" s="22"/>
+      <c r="J19" s="19"/>
       <c r="L19" s="2"/>
     </row>
     <row r="20" s="3" customFormat="1" spans="1:12">
-      <c r="A20" s="19">
+      <c r="A20" s="20">
         <v>26</v>
       </c>
-      <c r="B20" s="19">
+      <c r="B20" s="20">
         <v>5</v>
       </c>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19">
-        <v>160</v>
-      </c>
-      <c r="E20" s="19" t="s">
+      <c r="C20" s="20"/>
+      <c r="D20" s="20">
+        <v>150</v>
+      </c>
+      <c r="E20" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="F20" s="19">
-        <v>753</v>
-      </c>
-      <c r="G20" s="20" t="s">
+      <c r="F20" s="20">
+        <v>893</v>
+      </c>
+      <c r="G20" s="21" t="s">
         <v>18</v>
       </c>
       <c r="H20" s="18"/>
       <c r="I20" s="18"/>
-      <c r="J20" s="22"/>
+      <c r="J20" s="19"/>
       <c r="L20" s="2"/>
     </row>
     <row r="21" s="3" customFormat="1" spans="1:12">
-      <c r="A21" s="19">
+      <c r="A21" s="20">
         <v>27</v>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="20">
         <v>6</v>
       </c>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19">
+      <c r="C21" s="20"/>
+      <c r="D21" s="20">
         <v>200</v>
       </c>
-      <c r="E21" s="19" t="s">
+      <c r="E21" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="19">
-        <v>484</v>
-      </c>
-      <c r="G21" s="20" t="s">
+      <c r="F21" s="20">
+        <v>595</v>
+      </c>
+      <c r="G21" s="21" t="s">
         <v>18</v>
       </c>
       <c r="H21" s="18"/>
       <c r="I21" s="18"/>
-      <c r="J21" s="22"/>
+      <c r="J21" s="19"/>
       <c r="L21" s="2"/>
     </row>
     <row r="22" s="3" customFormat="1" spans="1:12">
-      <c r="A22" s="19">
+      <c r="A22" s="20">
         <v>28</v>
       </c>
-      <c r="B22" s="19">
+      <c r="B22" s="20">
         <v>7</v>
       </c>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19">
-        <v>240</v>
-      </c>
-      <c r="E22" s="19" t="s">
+      <c r="C22" s="20"/>
+      <c r="D22" s="20">
+        <v>400</v>
+      </c>
+      <c r="E22" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="F22" s="19">
-        <v>350</v>
-      </c>
-      <c r="G22" s="20" t="s">
+      <c r="F22" s="20">
+        <v>149</v>
+      </c>
+      <c r="G22" s="21" t="s">
         <v>18</v>
       </c>
       <c r="H22" s="18"/>
       <c r="I22" s="18"/>
-      <c r="J22" s="22"/>
+      <c r="J22" s="19"/>
       <c r="L22" s="2"/>
     </row>
     <row r="23" s="3" customFormat="1" spans="1:12">
-      <c r="A23" s="19">
+      <c r="A23" s="20">
         <v>29</v>
       </c>
-      <c r="B23" s="19">
+      <c r="B23" s="20">
         <v>8</v>
       </c>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19">
-        <v>280</v>
-      </c>
-      <c r="E23" s="19" t="s">
+      <c r="C23" s="20"/>
+      <c r="D23" s="20">
+        <v>600</v>
+      </c>
+      <c r="E23" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="F23" s="19">
-        <v>215</v>
-      </c>
-      <c r="G23" s="20" t="s">
+      <c r="F23" s="20">
+        <v>30</v>
+      </c>
+      <c r="G23" s="21" t="s">
         <v>18</v>
       </c>
       <c r="H23" s="18"/>
@@ -1807,23 +1807,23 @@
       <c r="L23" s="2"/>
     </row>
     <row r="24" s="3" customFormat="1" spans="1:12">
-      <c r="A24" s="19">
+      <c r="A24" s="20">
         <v>30</v>
       </c>
-      <c r="B24" s="19">
+      <c r="B24" s="20">
         <v>9</v>
       </c>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19">
-        <v>320</v>
-      </c>
-      <c r="E24" s="19" t="s">
+      <c r="C24" s="20"/>
+      <c r="D24" s="20">
+        <v>1200</v>
+      </c>
+      <c r="E24" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="F24" s="19">
-        <v>108</v>
-      </c>
-      <c r="G24" s="20" t="s">
+      <c r="F24" s="20">
+        <v>0</v>
+      </c>
+      <c r="G24" s="21" t="s">
         <v>18</v>
       </c>
       <c r="H24" s="18"/>
@@ -1831,91 +1831,91 @@
       <c r="J24" s="6"/>
       <c r="L24" s="2"/>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:12">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
-      <c r="G25" s="21"/>
+      <c r="G25" s="22"/>
       <c r="H25" s="18"/>
       <c r="I25" s="18"/>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:12">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
-      <c r="G26" s="21"/>
+      <c r="G26" s="22"/>
       <c r="H26" s="18"/>
       <c r="I26" s="18"/>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:12">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
-      <c r="G27" s="21"/>
+      <c r="G27" s="22"/>
       <c r="H27" s="18"/>
       <c r="I27" s="18"/>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:12">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
-      <c r="G28" s="21"/>
+      <c r="G28" s="22"/>
       <c r="H28" s="18"/>
       <c r="I28" s="18"/>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:12">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
-      <c r="G29" s="21"/>
+      <c r="G29" s="22"/>
       <c r="H29" s="18"/>
       <c r="I29" s="18"/>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:12">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
-      <c r="G30" s="21"/>
+      <c r="G30" s="22"/>
       <c r="H30" s="18"/>
       <c r="I30" s="18"/>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:12">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
-      <c r="G31" s="21"/>
+      <c r="G31" s="22"/>
       <c r="H31" s="18"/>
       <c r="I31" s="18"/>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:12">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
-      <c r="G32" s="21"/>
+      <c r="G32" s="22"/>
       <c r="H32" s="18"/>
       <c r="I32" s="18"/>
     </row>
@@ -1926,7 +1926,7 @@
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
-      <c r="G33" s="21"/>
+      <c r="G33" s="22"/>
       <c r="H33" s="18"/>
       <c r="I33" s="18"/>
     </row>
@@ -1937,7 +1937,7 @@
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
-      <c r="G34" s="21"/>
+      <c r="G34" s="22"/>
       <c r="H34" s="18"/>
       <c r="I34" s="18"/>
     </row>
@@ -1948,7 +1948,7 @@
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
-      <c r="G35" s="21"/>
+      <c r="G35" s="22"/>
       <c r="H35" s="18"/>
       <c r="I35" s="18"/>
     </row>
@@ -1959,7 +1959,7 @@
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
-      <c r="G36" s="21"/>
+      <c r="G36" s="22"/>
       <c r="H36" s="18"/>
       <c r="I36" s="18"/>
     </row>
@@ -1970,7 +1970,7 @@
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
-      <c r="G37" s="21"/>
+      <c r="G37" s="22"/>
       <c r="H37" s="18"/>
       <c r="I37" s="18"/>
     </row>
@@ -1981,7 +1981,7 @@
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
-      <c r="G38" s="21"/>
+      <c r="G38" s="22"/>
       <c r="H38" s="18"/>
       <c r="I38" s="18"/>
     </row>
@@ -1992,41 +1992,41 @@
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
-      <c r="G39" s="21"/>
+      <c r="G39" s="22"/>
       <c r="H39" s="18"/>
       <c r="I39" s="18"/>
     </row>
-    <row r="40" spans="3:6">
+    <row r="40" spans="1:9">
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
     </row>
-    <row r="41" spans="3:6">
+    <row r="41" spans="1:9">
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
     </row>
-    <row r="42" spans="3:6">
+    <row r="42" spans="1:9">
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
     </row>
-    <row r="43" spans="3:6">
+    <row r="43" spans="1:9">
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
     </row>
-    <row r="44" spans="3:6">
+    <row r="44" spans="1:9">
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
     </row>
-    <row r="45" spans="3:6">
+    <row r="45" spans="1:9">
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>

--- a/table/resources/sample/PointsAwardTurntable.xlsx
+++ b/table/resources/sample/PointsAwardTurntable.xlsx
@@ -1392,7 +1392,7 @@
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E6" s="16" t="s">
         <v>17</v>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="C7" s="16"/>
       <c r="D7" s="16">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>17</v>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="C8" s="16"/>
       <c r="D8" s="16">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E8" s="16" t="s">
         <v>17</v>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C9" s="16"/>
       <c r="D9" s="16">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E9" s="16" t="s">
         <v>17</v>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="C10" s="16"/>
       <c r="D10" s="16">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E10" s="16" t="s">
         <v>17</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="C11" s="16"/>
       <c r="D11" s="16">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E11" s="16" t="s">
         <v>17</v>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="C12" s="16"/>
       <c r="D12" s="16">
-        <v>400</v>
+        <v>386</v>
       </c>
       <c r="E12" s="16" t="s">
         <v>17</v>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="C13" s="16"/>
       <c r="D13" s="16">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="E13" s="16" t="s">
         <v>17</v>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="C14" s="16"/>
       <c r="D14" s="16">
-        <v>1200</v>
+        <v>1288</v>
       </c>
       <c r="E14" s="16" t="s">
         <v>17</v>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="20">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E16" s="20" t="s">
         <v>17</v>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="C17" s="20"/>
       <c r="D17" s="20">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="E17" s="20" t="s">
         <v>17</v>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="C18" s="20"/>
       <c r="D18" s="20">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E18" s="20" t="s">
         <v>17</v>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="20">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E19" s="20" t="s">
         <v>17</v>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="20">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E20" s="20" t="s">
         <v>17</v>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="20">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E21" s="20" t="s">
         <v>17</v>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="20">
-        <v>400</v>
+        <v>386</v>
       </c>
       <c r="E22" s="20" t="s">
         <v>17</v>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="C23" s="20"/>
       <c r="D23" s="20">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="E23" s="20" t="s">
         <v>17</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="C24" s="20"/>
       <c r="D24" s="20">
-        <v>1200</v>
+        <v>1288</v>
       </c>
       <c r="E24" s="20" t="s">
         <v>17</v>

--- a/table/resources/sample/PointsAwardTurntable.xlsx
+++ b/table/resources/sample/PointsAwardTurntable.xlsx
@@ -918,6 +918,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -925,9 +928,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1283,7 +1283,7 @@
     <col min="11" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:12">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1306,7 +1306,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:12">
       <c r="A2" s="7" t="s">
         <v>7</v>
       </c>
@@ -1329,7 +1329,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:12">
       <c r="A3" s="7" t="s">
         <v>10</v>
       </c>
@@ -1352,7 +1352,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:12">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -1361,7 +1361,7 @@
       <c r="F4" s="7"/>
       <c r="G4" s="11"/>
     </row>
-    <row r="5" s="2" customFormat="1" spans="1:10">
+    <row r="5" s="2" customFormat="1" spans="1:12">
       <c r="A5" s="16">
         <v>1</v>
       </c>
@@ -1376,14 +1376,14 @@
         <v>17</v>
       </c>
       <c r="F5" s="16">
-        <v>2421</v>
+        <v>1786</v>
       </c>
       <c r="G5" s="17"/>
       <c r="H5" s="18"/>
       <c r="I5" s="18"/>
       <c r="J5" s="18"/>
     </row>
-    <row r="6" s="2" customFormat="1" spans="1:10">
+    <row r="6" s="2" customFormat="1" spans="1:12">
       <c r="A6" s="16">
         <v>2</v>
       </c>
@@ -1392,20 +1392,20 @@
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="16">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E6" s="16" t="s">
         <v>17</v>
       </c>
       <c r="F6" s="16">
-        <v>2017</v>
+        <v>1786</v>
       </c>
       <c r="G6" s="17"/>
       <c r="H6" s="18"/>
       <c r="I6" s="18"/>
       <c r="J6" s="18"/>
     </row>
-    <row r="7" s="2" customFormat="1" spans="1:10">
+    <row r="7" s="2" customFormat="1" spans="1:12">
       <c r="A7" s="16">
         <v>3</v>
       </c>
@@ -1414,20 +1414,20 @@
       </c>
       <c r="C7" s="16"/>
       <c r="D7" s="16">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>17</v>
       </c>
       <c r="F7" s="16">
-        <v>1513</v>
+        <v>1786</v>
       </c>
       <c r="G7" s="17"/>
       <c r="H7" s="18"/>
       <c r="I7" s="18"/>
       <c r="J7" s="18"/>
     </row>
-    <row r="8" s="2" customFormat="1" spans="1:10">
+    <row r="8" s="2" customFormat="1" spans="1:12">
       <c r="A8" s="16">
         <v>4</v>
       </c>
@@ -1436,13 +1436,13 @@
       </c>
       <c r="C8" s="16"/>
       <c r="D8" s="16">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E8" s="16" t="s">
         <v>17</v>
       </c>
       <c r="F8" s="16">
-        <v>1210</v>
+        <v>1488</v>
       </c>
       <c r="G8" s="17"/>
       <c r="H8" s="18"/>
@@ -1458,18 +1458,18 @@
       </c>
       <c r="C9" s="16"/>
       <c r="D9" s="16">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E9" s="16" t="s">
         <v>17</v>
       </c>
       <c r="F9" s="16">
-        <v>928</v>
+        <v>1488</v>
       </c>
       <c r="G9" s="17"/>
       <c r="H9" s="18"/>
       <c r="I9" s="18"/>
-      <c r="J9" s="22"/>
+      <c r="J9" s="19"/>
       <c r="L9" s="2"/>
     </row>
     <row r="10" s="3" customFormat="1" spans="1:12">
@@ -1481,18 +1481,18 @@
       </c>
       <c r="C10" s="16"/>
       <c r="D10" s="16">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="E10" s="16" t="s">
         <v>17</v>
       </c>
       <c r="F10" s="16">
-        <v>753</v>
+        <v>893</v>
       </c>
       <c r="G10" s="17"/>
       <c r="H10" s="18"/>
       <c r="I10" s="18"/>
-      <c r="J10" s="22"/>
+      <c r="J10" s="19"/>
       <c r="L10" s="2"/>
     </row>
     <row r="11" s="3" customFormat="1" spans="1:12">
@@ -1504,18 +1504,18 @@
       </c>
       <c r="C11" s="16"/>
       <c r="D11" s="16">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E11" s="16" t="s">
         <v>17</v>
       </c>
       <c r="F11" s="16">
-        <v>484</v>
+        <v>595</v>
       </c>
       <c r="G11" s="17"/>
       <c r="H11" s="18"/>
       <c r="I11" s="18"/>
-      <c r="J11" s="22"/>
+      <c r="J11" s="19"/>
       <c r="L11" s="2"/>
     </row>
     <row r="12" s="3" customFormat="1" spans="1:12">
@@ -1527,18 +1527,18 @@
       </c>
       <c r="C12" s="16"/>
       <c r="D12" s="16">
-        <v>240</v>
+        <v>386</v>
       </c>
       <c r="E12" s="16" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="16">
-        <v>350</v>
+        <v>149</v>
       </c>
       <c r="G12" s="17"/>
       <c r="H12" s="18"/>
       <c r="I12" s="18"/>
-      <c r="J12" s="22"/>
+      <c r="J12" s="19"/>
       <c r="L12" s="2"/>
     </row>
     <row r="13" spans="1:12">
@@ -1550,13 +1550,13 @@
       </c>
       <c r="C13" s="16"/>
       <c r="D13" s="16">
-        <v>280</v>
+        <v>598</v>
       </c>
       <c r="E13" s="16" t="s">
         <v>17</v>
       </c>
       <c r="F13" s="16">
-        <v>215</v>
+        <v>30</v>
       </c>
       <c r="G13" s="17"/>
       <c r="H13" s="18"/>
@@ -1572,109 +1572,109 @@
       </c>
       <c r="C14" s="16"/>
       <c r="D14" s="16">
-        <v>320</v>
+        <v>1288</v>
       </c>
       <c r="E14" s="16" t="s">
         <v>17</v>
       </c>
       <c r="F14" s="16">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="G14" s="17"/>
       <c r="H14" s="18"/>
       <c r="I14" s="18"/>
       <c r="L14" s="2"/>
     </row>
-    <row r="15" s="2" customFormat="1" spans="1:10">
-      <c r="A15" s="19">
+    <row r="15" s="2" customFormat="1" spans="1:12">
+      <c r="A15" s="20">
         <v>21</v>
       </c>
-      <c r="B15" s="19">
+      <c r="B15" s="20">
         <v>0</v>
       </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19">
+      <c r="C15" s="20"/>
+      <c r="D15" s="20">
         <v>50</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="19">
-        <v>2421</v>
-      </c>
-      <c r="G15" s="20" t="s">
+      <c r="F15" s="20">
+        <v>1786</v>
+      </c>
+      <c r="G15" s="21" t="s">
         <v>18</v>
       </c>
       <c r="H15" s="18"/>
       <c r="I15" s="18"/>
       <c r="J15" s="18"/>
     </row>
-    <row r="16" s="2" customFormat="1" spans="1:10">
-      <c r="A16" s="19">
+    <row r="16" s="2" customFormat="1" spans="1:12">
+      <c r="A16" s="20">
         <v>22</v>
       </c>
-      <c r="B16" s="19">
+      <c r="B16" s="20">
         <v>1</v>
       </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19">
-        <v>60</v>
-      </c>
-      <c r="E16" s="19" t="s">
+      <c r="C16" s="20"/>
+      <c r="D16" s="20">
+        <v>66</v>
+      </c>
+      <c r="E16" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="F16" s="19">
-        <v>2017</v>
-      </c>
-      <c r="G16" s="20" t="s">
+      <c r="F16" s="20">
+        <v>1786</v>
+      </c>
+      <c r="G16" s="21" t="s">
         <v>18</v>
       </c>
       <c r="H16" s="18"/>
       <c r="I16" s="18"/>
       <c r="J16" s="18"/>
     </row>
-    <row r="17" s="2" customFormat="1" spans="1:10">
-      <c r="A17" s="19">
+    <row r="17" s="2" customFormat="1" spans="1:12">
+      <c r="A17" s="20">
         <v>23</v>
       </c>
-      <c r="B17" s="19">
+      <c r="B17" s="20">
         <v>2</v>
       </c>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19">
-        <v>80</v>
-      </c>
-      <c r="E17" s="19" t="s">
+      <c r="C17" s="20"/>
+      <c r="D17" s="20">
+        <v>88</v>
+      </c>
+      <c r="E17" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="F17" s="19">
-        <v>1513</v>
-      </c>
-      <c r="G17" s="20" t="s">
+      <c r="F17" s="20">
+        <v>1786</v>
+      </c>
+      <c r="G17" s="21" t="s">
         <v>18</v>
       </c>
       <c r="H17" s="18"/>
       <c r="I17" s="18"/>
       <c r="J17" s="18"/>
     </row>
-    <row r="18" s="2" customFormat="1" spans="1:10">
-      <c r="A18" s="19">
+    <row r="18" s="2" customFormat="1" spans="1:12">
+      <c r="A18" s="20">
         <v>24</v>
       </c>
-      <c r="B18" s="19">
+      <c r="B18" s="20">
         <v>3</v>
       </c>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19">
-        <v>100</v>
-      </c>
-      <c r="E18" s="19" t="s">
+      <c r="C18" s="20"/>
+      <c r="D18" s="20">
+        <v>102</v>
+      </c>
+      <c r="E18" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="F18" s="19">
-        <v>1210</v>
-      </c>
-      <c r="G18" s="20" t="s">
+      <c r="F18" s="20">
+        <v>1488</v>
+      </c>
+      <c r="G18" s="21" t="s">
         <v>18</v>
       </c>
       <c r="H18" s="18"/>
@@ -1682,123 +1682,123 @@
       <c r="J18" s="18"/>
     </row>
     <row r="19" s="3" customFormat="1" spans="1:12">
-      <c r="A19" s="19">
+      <c r="A19" s="20">
         <v>25</v>
       </c>
-      <c r="B19" s="19">
+      <c r="B19" s="20">
         <v>4</v>
       </c>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19">
-        <v>130</v>
-      </c>
-      <c r="E19" s="19" t="s">
+      <c r="C19" s="20"/>
+      <c r="D19" s="20">
+        <v>125</v>
+      </c>
+      <c r="E19" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="F19" s="19">
-        <v>928</v>
-      </c>
-      <c r="G19" s="20" t="s">
+      <c r="F19" s="20">
+        <v>1488</v>
+      </c>
+      <c r="G19" s="21" t="s">
         <v>18</v>
       </c>
       <c r="H19" s="18"/>
       <c r="I19" s="18"/>
-      <c r="J19" s="22"/>
+      <c r="J19" s="19"/>
       <c r="L19" s="2"/>
     </row>
     <row r="20" s="3" customFormat="1" spans="1:12">
-      <c r="A20" s="19">
+      <c r="A20" s="20">
         <v>26</v>
       </c>
-      <c r="B20" s="19">
+      <c r="B20" s="20">
         <v>5</v>
       </c>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19">
-        <v>160</v>
-      </c>
-      <c r="E20" s="19" t="s">
+      <c r="C20" s="20"/>
+      <c r="D20" s="20">
+        <v>148</v>
+      </c>
+      <c r="E20" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="F20" s="19">
-        <v>753</v>
-      </c>
-      <c r="G20" s="20" t="s">
+      <c r="F20" s="20">
+        <v>893</v>
+      </c>
+      <c r="G20" s="21" t="s">
         <v>18</v>
       </c>
       <c r="H20" s="18"/>
       <c r="I20" s="18"/>
-      <c r="J20" s="22"/>
+      <c r="J20" s="19"/>
       <c r="L20" s="2"/>
     </row>
     <row r="21" s="3" customFormat="1" spans="1:12">
-      <c r="A21" s="19">
+      <c r="A21" s="20">
         <v>27</v>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="20">
         <v>6</v>
       </c>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19">
-        <v>200</v>
-      </c>
-      <c r="E21" s="19" t="s">
+      <c r="C21" s="20"/>
+      <c r="D21" s="20">
+        <v>198</v>
+      </c>
+      <c r="E21" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="F21" s="19">
-        <v>484</v>
-      </c>
-      <c r="G21" s="20" t="s">
+      <c r="F21" s="20">
+        <v>595</v>
+      </c>
+      <c r="G21" s="21" t="s">
         <v>18</v>
       </c>
       <c r="H21" s="18"/>
       <c r="I21" s="18"/>
-      <c r="J21" s="22"/>
+      <c r="J21" s="19"/>
       <c r="L21" s="2"/>
     </row>
     <row r="22" s="3" customFormat="1" spans="1:12">
-      <c r="A22" s="19">
+      <c r="A22" s="20">
         <v>28</v>
       </c>
-      <c r="B22" s="19">
+      <c r="B22" s="20">
         <v>7</v>
       </c>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19">
-        <v>240</v>
-      </c>
-      <c r="E22" s="19" t="s">
+      <c r="C22" s="20"/>
+      <c r="D22" s="20">
+        <v>386</v>
+      </c>
+      <c r="E22" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="F22" s="19">
-        <v>350</v>
-      </c>
-      <c r="G22" s="20" t="s">
+      <c r="F22" s="20">
+        <v>149</v>
+      </c>
+      <c r="G22" s="21" t="s">
         <v>18</v>
       </c>
       <c r="H22" s="18"/>
       <c r="I22" s="18"/>
-      <c r="J22" s="22"/>
+      <c r="J22" s="19"/>
       <c r="L22" s="2"/>
     </row>
     <row r="23" s="3" customFormat="1" spans="1:12">
-      <c r="A23" s="19">
+      <c r="A23" s="20">
         <v>29</v>
       </c>
-      <c r="B23" s="19">
+      <c r="B23" s="20">
         <v>8</v>
       </c>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19">
-        <v>280</v>
-      </c>
-      <c r="E23" s="19" t="s">
+      <c r="C23" s="20"/>
+      <c r="D23" s="20">
+        <v>598</v>
+      </c>
+      <c r="E23" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="F23" s="19">
-        <v>215</v>
-      </c>
-      <c r="G23" s="20" t="s">
+      <c r="F23" s="20">
+        <v>30</v>
+      </c>
+      <c r="G23" s="21" t="s">
         <v>18</v>
       </c>
       <c r="H23" s="18"/>
@@ -1807,23 +1807,23 @@
       <c r="L23" s="2"/>
     </row>
     <row r="24" s="3" customFormat="1" spans="1:12">
-      <c r="A24" s="19">
+      <c r="A24" s="20">
         <v>30</v>
       </c>
-      <c r="B24" s="19">
+      <c r="B24" s="20">
         <v>9</v>
       </c>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19">
-        <v>320</v>
-      </c>
-      <c r="E24" s="19" t="s">
+      <c r="C24" s="20"/>
+      <c r="D24" s="20">
+        <v>1288</v>
+      </c>
+      <c r="E24" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="F24" s="19">
-        <v>108</v>
-      </c>
-      <c r="G24" s="20" t="s">
+      <c r="F24" s="20">
+        <v>0</v>
+      </c>
+      <c r="G24" s="21" t="s">
         <v>18</v>
       </c>
       <c r="H24" s="18"/>
@@ -1831,91 +1831,91 @@
       <c r="J24" s="6"/>
       <c r="L24" s="2"/>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:12">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
-      <c r="G25" s="21"/>
+      <c r="G25" s="22"/>
       <c r="H25" s="18"/>
       <c r="I25" s="18"/>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:12">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
-      <c r="G26" s="21"/>
+      <c r="G26" s="22"/>
       <c r="H26" s="18"/>
       <c r="I26" s="18"/>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:12">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
-      <c r="G27" s="21"/>
+      <c r="G27" s="22"/>
       <c r="H27" s="18"/>
       <c r="I27" s="18"/>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:12">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
-      <c r="G28" s="21"/>
+      <c r="G28" s="22"/>
       <c r="H28" s="18"/>
       <c r="I28" s="18"/>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:12">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
-      <c r="G29" s="21"/>
+      <c r="G29" s="22"/>
       <c r="H29" s="18"/>
       <c r="I29" s="18"/>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:12">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
-      <c r="G30" s="21"/>
+      <c r="G30" s="22"/>
       <c r="H30" s="18"/>
       <c r="I30" s="18"/>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:12">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
-      <c r="G31" s="21"/>
+      <c r="G31" s="22"/>
       <c r="H31" s="18"/>
       <c r="I31" s="18"/>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:12">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
-      <c r="G32" s="21"/>
+      <c r="G32" s="22"/>
       <c r="H32" s="18"/>
       <c r="I32" s="18"/>
     </row>
@@ -1926,7 +1926,7 @@
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
-      <c r="G33" s="21"/>
+      <c r="G33" s="22"/>
       <c r="H33" s="18"/>
       <c r="I33" s="18"/>
     </row>
@@ -1937,7 +1937,7 @@
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
-      <c r="G34" s="21"/>
+      <c r="G34" s="22"/>
       <c r="H34" s="18"/>
       <c r="I34" s="18"/>
     </row>
@@ -1948,7 +1948,7 @@
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
-      <c r="G35" s="21"/>
+      <c r="G35" s="22"/>
       <c r="H35" s="18"/>
       <c r="I35" s="18"/>
     </row>
@@ -1959,7 +1959,7 @@
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
-      <c r="G36" s="21"/>
+      <c r="G36" s="22"/>
       <c r="H36" s="18"/>
       <c r="I36" s="18"/>
     </row>
@@ -1970,7 +1970,7 @@
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
-      <c r="G37" s="21"/>
+      <c r="G37" s="22"/>
       <c r="H37" s="18"/>
       <c r="I37" s="18"/>
     </row>
@@ -1981,7 +1981,7 @@
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
-      <c r="G38" s="21"/>
+      <c r="G38" s="22"/>
       <c r="H38" s="18"/>
       <c r="I38" s="18"/>
     </row>
@@ -1992,41 +1992,41 @@
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
-      <c r="G39" s="21"/>
+      <c r="G39" s="22"/>
       <c r="H39" s="18"/>
       <c r="I39" s="18"/>
     </row>
-    <row r="40" spans="3:6">
+    <row r="40" spans="1:9">
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
     </row>
-    <row r="41" spans="3:6">
+    <row r="41" spans="1:9">
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
     </row>
-    <row r="42" spans="3:6">
+    <row r="42" spans="1:9">
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
     </row>
-    <row r="43" spans="3:6">
+    <row r="43" spans="1:9">
       <c r="C43" s="2"/>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
     </row>
-    <row r="44" spans="3:6">
+    <row r="44" spans="1:9">
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
     </row>
-    <row r="45" spans="3:6">
+    <row r="45" spans="1:9">
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
